--- a/src/FDE_TST.xlsx
+++ b/src/FDE_TST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dar/Documents/bsa-delivery-service-case-study/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EE157E-5AD5-A446-9E5F-DC014FB8112B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B649148-89EE-B149-8FCF-A387B28F36E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{685818EC-EDD0-1A43-85F5-D270B6B7B403}"/>
   </bookViews>
@@ -766,5 +766,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>